--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -305,6 +305,60 @@
     <t>12000,1</t>
   </si>
   <si>
+    <t>1转天龙武器</t>
+  </si>
+  <si>
+    <t>1300,1</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
+    <t>1转天龙衣服</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>1转天龙首饰</t>
+  </si>
+  <si>
+    <t>13000,1</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>2转天龙武器</t>
+  </si>
+  <si>
+    <t>1400,1</t>
+  </si>
+  <si>
+    <t>2转天龙衣服</t>
+  </si>
+  <si>
+    <t>2转天龙首饰</t>
+  </si>
+  <si>
+    <t>14000,1</t>
+  </si>
+  <si>
+    <t>3转天龙武器</t>
+  </si>
+  <si>
+    <t>1500,1</t>
+  </si>
+  <si>
+    <t>3转天龙衣服</t>
+  </si>
+  <si>
+    <t>3转天龙首饰</t>
+  </si>
+  <si>
+    <t>15000,1</t>
+  </si>
+  <si>
     <t>落日平原</t>
   </si>
   <si>
@@ -416,9 +470,6 @@
     <t>Player/Boss/Boss10</t>
   </si>
   <si>
-    <t>10001</t>
-  </si>
-  <si>
     <t>生命倍率</t>
   </si>
   <si>
@@ -428,9 +479,6 @@
     <t>Player/Boss/Boss11</t>
   </si>
   <si>
-    <t>10002</t>
-  </si>
-  <si>
     <t>防御倍率</t>
   </si>
   <si>
@@ -438,9 +486,6 @@
   </si>
   <si>
     <t>Player/Boss/Boss12</t>
-  </si>
-  <si>
-    <t>10003</t>
   </si>
   <si>
     <t>攻击倍率</t>
@@ -1421,7 +1466,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N41"/>
+  <dimension ref="C1:N50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2769,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="1">
-        <f>J36+1</f>
+        <f t="shared" ref="J39:J43" si="5">J36+1</f>
         <v>13</v>
       </c>
       <c r="K39" s="1">
@@ -2805,7 +2850,7 @@
         <v>24</v>
       </c>
       <c r="J40" s="1">
-        <f>J37+1</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="K40" s="1">
@@ -2851,6 +2896,321 @@
         <v>5</v>
       </c>
       <c r="M41" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1">
+        <v>10</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J43" s="1">
+        <v>2</v>
+      </c>
+      <c r="K43" s="1">
+        <v>10</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J44" s="1">
+        <v>2</v>
+      </c>
+      <c r="K44" s="1">
+        <v>10</v>
+      </c>
+      <c r="L44" s="1">
+        <v>5</v>
+      </c>
+      <c r="M44" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="1">
+        <v>2</v>
+      </c>
+      <c r="K45" s="1">
+        <v>10</v>
+      </c>
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <v>2</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J46" s="1">
+        <v>2</v>
+      </c>
+      <c r="K46" s="1">
+        <v>10</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1">
+        <v>10</v>
+      </c>
+      <c r="L47" s="1">
+        <v>5</v>
+      </c>
+      <c r="M47" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J48" s="1">
+        <v>2</v>
+      </c>
+      <c r="K48" s="1">
+        <v>10</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:13">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <v>2</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1">
+        <v>10</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:13">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J50" s="1">
+        <v>2</v>
+      </c>
+      <c r="K50" s="1">
+        <v>10</v>
+      </c>
+      <c r="L50" s="1">
+        <v>5</v>
+      </c>
+      <c r="M50" s="1">
         <v>10</v>
       </c>
     </row>
@@ -3013,19 +3373,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
@@ -3040,7 +3400,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3051,19 +3411,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
@@ -3078,7 +3438,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3089,19 +3449,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
@@ -3116,7 +3476,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3127,19 +3487,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
@@ -3154,7 +3514,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3165,19 +3525,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -3192,7 +3552,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3203,19 +3563,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -3230,7 +3590,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3241,19 +3601,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3268,7 +3628,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3279,19 +3639,19 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="J13" s="1">
         <v>15</v>
@@ -3306,7 +3666,7 @@
         <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3317,19 +3677,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="J14" s="1">
         <v>15</v>
@@ -3344,7 +3704,7 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3355,19 +3715,19 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="J15" s="1">
         <v>5</v>
@@ -3382,7 +3742,7 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3393,19 +3753,19 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>131</v>
+        <v>94</v>
       </c>
       <c r="J16" s="1">
         <v>5</v>
@@ -3420,7 +3780,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3431,19 +3791,19 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="J17" s="1">
         <v>5</v>
@@ -3458,7 +3818,7 @@
         <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:14">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="153">
   <si>
     <t>#</t>
   </si>
@@ -489,6 +489,9 @@
   </si>
   <si>
     <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>狮王宠物</t>
   </si>
 </sst>
 </file>
@@ -3228,7 +3231,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N18"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3783,7 +3786,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C17" s="1">
         <v>1112</v>
       </c>
@@ -3821,8 +3824,197 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:14">
-      <c r="F18" s="2"/>
+    <row r="18" customHeight="1" spans="1:14">
+      <c r="C18" s="1">
+        <v>1113</v>
+      </c>
+      <c r="D18" s="1">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" s="1">
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
+        <v>20</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:14">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1114</v>
+      </c>
+      <c r="D19" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:14">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1115</v>
+      </c>
+      <c r="D20" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:14">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1116</v>
+      </c>
+      <c r="D21" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1117</v>
+      </c>
+      <c r="D22" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:14">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1118</v>
+      </c>
+      <c r="D23" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1119</v>
+      </c>
+      <c r="D24" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:14">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1120</v>
+      </c>
+      <c r="D25" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:14">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1121</v>
+      </c>
+      <c r="D26" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1122</v>
+      </c>
+      <c r="D27" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1123</v>
+      </c>
+      <c r="D28" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1124</v>
+      </c>
+      <c r="D29" s="1">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="装备图鉴" sheetId="2" r:id="rId1"/>
@@ -2934,7 +2934,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:13">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:13">
@@ -3004,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="M44" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:13">
@@ -3039,7 +3039,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:13">
@@ -3074,7 +3074,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
@@ -3109,7 +3109,7 @@
         <v>5</v>
       </c>
       <c r="M47" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:13">
@@ -3144,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="M48" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:13">
@@ -3179,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:13">
@@ -3214,7 +3214,7 @@
         <v>5</v>
       </c>
       <c r="M50" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="166">
   <si>
     <t>#</t>
   </si>
@@ -357,6 +357,45 @@
   </si>
   <si>
     <t>15000,1</t>
+  </si>
+  <si>
+    <t>4转天龙武器</t>
+  </si>
+  <si>
+    <t>4转天龙衣服</t>
+  </si>
+  <si>
+    <t>4转天龙首饰</t>
+  </si>
+  <si>
+    <t>20000,1</t>
+  </si>
+  <si>
+    <t>5转天龙武器</t>
+  </si>
+  <si>
+    <t>2500,1</t>
+  </si>
+  <si>
+    <t>5转天龙衣服</t>
+  </si>
+  <si>
+    <t>5转天龙首饰</t>
+  </si>
+  <si>
+    <t>25000,1</t>
+  </si>
+  <si>
+    <t>6转天龙武器</t>
+  </si>
+  <si>
+    <t>6转天龙衣服</t>
+  </si>
+  <si>
+    <t>6转天龙首饰</t>
+  </si>
+  <si>
+    <t>30000,1</t>
   </si>
   <si>
     <t>落日平原</t>
@@ -1469,7 +1508,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N50"/>
+  <dimension ref="C1:N59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3214,6 +3253,321 @@
         <v>5</v>
       </c>
       <c r="M50" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:13">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J51" s="1">
+        <v>2</v>
+      </c>
+      <c r="K51" s="1">
+        <v>10</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:13">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+      <c r="K52" s="1">
+        <v>10</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J53" s="1">
+        <v>2</v>
+      </c>
+      <c r="K53" s="1">
+        <v>10</v>
+      </c>
+      <c r="L53" s="1">
+        <v>5</v>
+      </c>
+      <c r="M53" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>10</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:13">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J55" s="1">
+        <v>2</v>
+      </c>
+      <c r="K55" s="1">
+        <v>10</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:13">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J56" s="1">
+        <v>2</v>
+      </c>
+      <c r="K56" s="1">
+        <v>10</v>
+      </c>
+      <c r="L56" s="1">
+        <v>5</v>
+      </c>
+      <c r="M56" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:13">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J57" s="1">
+        <v>2</v>
+      </c>
+      <c r="K57" s="1">
+        <v>10</v>
+      </c>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:13">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1">
+        <v>2</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J58" s="1">
+        <v>2</v>
+      </c>
+      <c r="K58" s="1">
+        <v>10</v>
+      </c>
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+      <c r="M58" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:13">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1">
+        <v>2</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" s="1">
+        <v>2</v>
+      </c>
+      <c r="K59" s="1">
+        <v>10</v>
+      </c>
+      <c r="L59" s="1">
+        <v>5</v>
+      </c>
+      <c r="M59" s="1">
         <v>15</v>
       </c>
     </row>
@@ -3376,19 +3730,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
@@ -3403,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3414,19 +3768,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
@@ -3441,7 +3795,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3452,19 +3806,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
@@ -3479,7 +3833,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3490,19 +3844,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>110</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
@@ -3517,7 +3871,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3528,19 +3882,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -3555,7 +3909,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3566,19 +3920,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -3593,7 +3947,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3604,19 +3958,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3631,7 +3985,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3642,19 +3996,19 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J13" s="1">
         <v>15</v>
@@ -3669,7 +4023,7 @@
         <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3680,19 +4034,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J14" s="1">
         <v>15</v>
@@ -3707,7 +4061,7 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3718,16 +4072,16 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>97</v>
@@ -3745,7 +4099,7 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3756,16 +4110,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>94</v>
@@ -3783,7 +4137,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3794,16 +4148,16 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>92</v>
@@ -3821,7 +4175,7 @@
         <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:14">
@@ -3832,16 +4186,16 @@
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>97</v>
@@ -3859,7 +4213,7 @@
         <v>20</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:14">

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="179">
   <si>
     <t>#</t>
   </si>
@@ -396,6 +396,45 @@
   </si>
   <si>
     <t>30000,1</t>
+  </si>
+  <si>
+    <t>7转天龙武器</t>
+  </si>
+  <si>
+    <t>3500,1</t>
+  </si>
+  <si>
+    <t>7转天龙衣服</t>
+  </si>
+  <si>
+    <t>7转天龙首饰</t>
+  </si>
+  <si>
+    <t>35000,1</t>
+  </si>
+  <si>
+    <t>8转天龙武器</t>
+  </si>
+  <si>
+    <t>8转天龙衣服</t>
+  </si>
+  <si>
+    <t>8转天龙首饰</t>
+  </si>
+  <si>
+    <t>40000,1</t>
+  </si>
+  <si>
+    <t>9转天龙武器</t>
+  </si>
+  <si>
+    <t>9转天龙衣服</t>
+  </si>
+  <si>
+    <t>9转天龙首饰</t>
+  </si>
+  <si>
+    <t>50000,1</t>
   </si>
   <si>
     <t>落日平原</t>
@@ -1508,7 +1547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N59"/>
+  <dimension ref="C1:N75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3570,6 +3609,342 @@
       <c r="M59" s="1">
         <v>15</v>
       </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:13">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1">
+        <v>2</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J60" s="1">
+        <v>2</v>
+      </c>
+      <c r="K60" s="1">
+        <v>10</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:13">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J61" s="1">
+        <v>2</v>
+      </c>
+      <c r="K61" s="1">
+        <v>10</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:13">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1">
+        <v>2</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J62" s="1">
+        <v>2</v>
+      </c>
+      <c r="K62" s="1">
+        <v>10</v>
+      </c>
+      <c r="L62" s="1">
+        <v>5</v>
+      </c>
+      <c r="M62" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:13">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J63" s="1">
+        <v>2</v>
+      </c>
+      <c r="K63" s="1">
+        <v>10</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:13">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1">
+        <v>2</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J64" s="1">
+        <v>2</v>
+      </c>
+      <c r="K64" s="1">
+        <v>10</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:13">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J65" s="1">
+        <v>2</v>
+      </c>
+      <c r="K65" s="1">
+        <v>10</v>
+      </c>
+      <c r="L65" s="1">
+        <v>5</v>
+      </c>
+      <c r="M65" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:13">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="1">
+        <v>2</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J66" s="1">
+        <v>2</v>
+      </c>
+      <c r="K66" s="1">
+        <v>10</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:13">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="1">
+        <v>2</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J67" s="1">
+        <v>2</v>
+      </c>
+      <c r="K67" s="1">
+        <v>10</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:13">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J68" s="1">
+        <v>2</v>
+      </c>
+      <c r="K68" s="1">
+        <v>10</v>
+      </c>
+      <c r="L68" s="1">
+        <v>5</v>
+      </c>
+      <c r="M68" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:13">
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" customHeight="1" spans="3:13">
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" customHeight="1" spans="3:13">
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" customHeight="1" spans="3:13">
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" customHeight="1" spans="3:13">
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" customHeight="1" spans="3:13">
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" customHeight="1" spans="3:13">
+      <c r="F75" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3730,19 +4105,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J6" s="1">
         <v>3</v>
@@ -3757,7 +4132,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3768,19 +4143,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
@@ -3795,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3806,19 +4181,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="J8" s="1">
         <v>5</v>
@@ -3833,7 +4208,7 @@
         <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3844,19 +4219,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>123</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
@@ -3871,7 +4246,7 @@
         <v>8</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3882,19 +4257,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J10" s="1">
         <v>10</v>
@@ -3909,7 +4284,7 @@
         <v>9</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3920,19 +4295,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J11" s="1">
         <v>10</v>
@@ -3947,7 +4322,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3958,19 +4333,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J12" s="1">
         <v>10</v>
@@ -3985,7 +4360,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -3996,19 +4371,19 @@
         <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J13" s="1">
         <v>15</v>
@@ -4023,7 +4398,7 @@
         <v>12</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -4034,19 +4409,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="J14" s="1">
         <v>15</v>
@@ -4061,7 +4436,7 @@
         <v>13</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -4072,16 +4447,16 @@
         <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>97</v>
@@ -4099,7 +4474,7 @@
         <v>14</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -4110,16 +4485,16 @@
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>94</v>
@@ -4137,7 +4512,7 @@
         <v>15</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -4148,16 +4523,16 @@
         <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>92</v>
@@ -4175,7 +4550,7 @@
         <v>16</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:14">
@@ -4186,16 +4561,16 @@
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>97</v>
@@ -4213,7 +4588,7 @@
         <v>20</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:14">
